--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-nebenwirkung-meddra-sct.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-nebenwirkung-meddra-sct.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="2594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="2585">
   <si>
     <t>Property</t>
   </si>
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://snomed.info/sct?fhir_vs</t>
+    <t>http://snomed.info/sct/900000000000207008/version/20250701?fhir_vs</t>
   </si>
   <si>
     <t>Display</t>
@@ -120,7 +120,7 @@
     <t/>
   </si>
   <si>
-    <t>http://snomed.info/sct</t>
+    <t>http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20250701</t>
   </si>
   <si>
     <t>10000060</t>
@@ -5673,10 +5673,10 @@
     <t>Prostate infection</t>
   </si>
   <si>
-    <t>1371408008</t>
-  </si>
-  <si>
-    <t>Infection of prostate</t>
+    <t>9713002</t>
+  </si>
+  <si>
+    <t>Prostatitis</t>
   </si>
   <si>
     <t>10050816</t>
@@ -5793,10 +5793,7 @@
     <t>Cytokine release syndrome</t>
   </si>
   <si>
-    <t>891589671000119104</t>
-  </si>
-  <si>
-    <t>Cytokine storm syndrome</t>
+    <t>710027002</t>
   </si>
   <si>
     <t>10052298</t>
@@ -7179,18 +7176,6 @@
     <t>Hemorrhage of cecum</t>
   </si>
   <si>
-    <t>10065748</t>
-  </si>
-  <si>
-    <t>Urostomy site bleeding</t>
-  </si>
-  <si>
-    <t>16751421000119105</t>
-  </si>
-  <si>
-    <t>Hemorrhage of incontinent urostomy stoma</t>
-  </si>
-  <si>
     <t>10065749</t>
   </si>
   <si>
@@ -7542,12 +7527,6 @@
     <t>Intraoperative arterial injury</t>
   </si>
   <si>
-    <t>1375944001</t>
-  </si>
-  <si>
-    <t>Traumatic injury to artery during surgery</t>
-  </si>
-  <si>
     <t>10065827</t>
   </si>
   <si>
@@ -7602,10 +7581,10 @@
     <t>Intraoperative renal injury</t>
   </si>
   <si>
-    <t>1375936001</t>
-  </si>
-  <si>
-    <t>Traumatic injury to kidney during surgery</t>
+    <t>40095003</t>
+  </si>
+  <si>
+    <t>Injury of kidney</t>
   </si>
   <si>
     <t>10065847</t>
@@ -7624,12 +7603,6 @@
   </si>
   <si>
     <t>Intraoperative venous injury</t>
-  </si>
-  <si>
-    <t>1375937005</t>
-  </si>
-  <si>
-    <t>Traumatic injury to vein during surgery</t>
   </si>
   <si>
     <t>10065849</t>
@@ -8068,7 +8041,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E710"/>
+  <dimension ref="A1:E709"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16902,7 +16875,7 @@
         <v>1885</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D520" t="s" s="2">
         <v>1886</v>
@@ -17095,1987 +17068,1987 @@
         <v>1926</v>
       </c>
       <c r="E531" t="s" s="2">
-        <v>1927</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
+        <v>1927</v>
+      </c>
+      <c r="B532" t="s" s="2">
         <v>1928</v>
       </c>
-      <c r="B532" t="s" s="2">
+      <c r="C532" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D532" t="s" s="2">
         <v>1929</v>
       </c>
-      <c r="C532" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D532" t="s" s="2">
+      <c r="E532" t="s" s="2">
         <v>1930</v>
-      </c>
-      <c r="E532" t="s" s="2">
-        <v>1931</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
+        <v>1931</v>
+      </c>
+      <c r="B533" t="s" s="2">
         <v>1932</v>
       </c>
-      <c r="B533" t="s" s="2">
+      <c r="C533" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D533" t="s" s="2">
         <v>1933</v>
       </c>
-      <c r="C533" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D533" t="s" s="2">
+      <c r="E533" t="s" s="2">
         <v>1934</v>
-      </c>
-      <c r="E533" t="s" s="2">
-        <v>1935</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
+        <v>1935</v>
+      </c>
+      <c r="B534" t="s" s="2">
         <v>1936</v>
       </c>
-      <c r="B534" t="s" s="2">
+      <c r="C534" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D534" t="s" s="2">
         <v>1937</v>
       </c>
-      <c r="C534" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D534" t="s" s="2">
-        <v>1938</v>
-      </c>
       <c r="E534" t="s" s="2">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
+        <v>1938</v>
+      </c>
+      <c r="B535" t="s" s="2">
         <v>1939</v>
       </c>
-      <c r="B535" t="s" s="2">
+      <c r="C535" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D535" t="s" s="2">
         <v>1940</v>
       </c>
-      <c r="C535" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D535" t="s" s="2">
+      <c r="E535" t="s" s="2">
         <v>1941</v>
-      </c>
-      <c r="E535" t="s" s="2">
-        <v>1942</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
+        <v>1942</v>
+      </c>
+      <c r="B536" t="s" s="2">
         <v>1943</v>
       </c>
-      <c r="B536" t="s" s="2">
+      <c r="C536" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D536" t="s" s="2">
         <v>1944</v>
       </c>
-      <c r="C536" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D536" t="s" s="2">
+      <c r="E536" t="s" s="2">
         <v>1945</v>
-      </c>
-      <c r="E536" t="s" s="2">
-        <v>1946</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
+        <v>1946</v>
+      </c>
+      <c r="B537" t="s" s="2">
         <v>1947</v>
       </c>
-      <c r="B537" t="s" s="2">
+      <c r="C537" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D537" t="s" s="2">
         <v>1948</v>
       </c>
-      <c r="C537" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D537" t="s" s="2">
+      <c r="E537" t="s" s="2">
         <v>1949</v>
-      </c>
-      <c r="E537" t="s" s="2">
-        <v>1950</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
+        <v>1950</v>
+      </c>
+      <c r="B538" t="s" s="2">
         <v>1951</v>
       </c>
-      <c r="B538" t="s" s="2">
+      <c r="C538" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D538" t="s" s="2">
         <v>1952</v>
       </c>
-      <c r="C538" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D538" t="s" s="2">
-        <v>1953</v>
-      </c>
       <c r="E538" t="s" s="2">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
+        <v>1953</v>
+      </c>
+      <c r="B539" t="s" s="2">
         <v>1954</v>
-      </c>
-      <c r="B539" t="s" s="2">
-        <v>1955</v>
       </c>
       <c r="C539" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D539" t="s" s="2">
+        <v>1955</v>
+      </c>
+      <c r="E539" t="s" s="2">
         <v>1956</v>
-      </c>
-      <c r="E539" t="s" s="2">
-        <v>1957</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
+        <v>1957</v>
+      </c>
+      <c r="B540" t="s" s="2">
         <v>1958</v>
-      </c>
-      <c r="B540" t="s" s="2">
-        <v>1959</v>
       </c>
       <c r="C540" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D540" t="s" s="2">
+        <v>1959</v>
+      </c>
+      <c r="E540" t="s" s="2">
         <v>1960</v>
-      </c>
-      <c r="E540" t="s" s="2">
-        <v>1961</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
+        <v>1961</v>
+      </c>
+      <c r="B541" t="s" s="2">
         <v>1962</v>
-      </c>
-      <c r="B541" t="s" s="2">
-        <v>1963</v>
       </c>
       <c r="C541" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D541" t="s" s="2">
+        <v>1963</v>
+      </c>
+      <c r="E541" t="s" s="2">
         <v>1964</v>
-      </c>
-      <c r="E541" t="s" s="2">
-        <v>1965</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
+        <v>1965</v>
+      </c>
+      <c r="B542" t="s" s="2">
         <v>1966</v>
       </c>
-      <c r="B542" t="s" s="2">
+      <c r="C542" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D542" t="s" s="2">
         <v>1967</v>
       </c>
-      <c r="C542" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D542" t="s" s="2">
+      <c r="E542" t="s" s="2">
         <v>1968</v>
-      </c>
-      <c r="E542" t="s" s="2">
-        <v>1969</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
+        <v>1969</v>
+      </c>
+      <c r="B543" t="s" s="2">
         <v>1970</v>
       </c>
-      <c r="B543" t="s" s="2">
+      <c r="C543" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D543" t="s" s="2">
         <v>1971</v>
       </c>
-      <c r="C543" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D543" t="s" s="2">
-        <v>1972</v>
-      </c>
       <c r="E543" t="s" s="2">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
+        <v>1972</v>
+      </c>
+      <c r="B544" t="s" s="2">
         <v>1973</v>
-      </c>
-      <c r="B544" t="s" s="2">
-        <v>1974</v>
       </c>
       <c r="C544" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D544" t="s" s="2">
+        <v>1974</v>
+      </c>
+      <c r="E544" t="s" s="2">
         <v>1975</v>
-      </c>
-      <c r="E544" t="s" s="2">
-        <v>1976</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
+        <v>1976</v>
+      </c>
+      <c r="B545" t="s" s="2">
         <v>1977</v>
       </c>
-      <c r="B545" t="s" s="2">
+      <c r="C545" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D545" t="s" s="2">
         <v>1978</v>
       </c>
-      <c r="C545" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D545" t="s" s="2">
+      <c r="E545" t="s" s="2">
         <v>1979</v>
-      </c>
-      <c r="E545" t="s" s="2">
-        <v>1980</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
+        <v>1980</v>
+      </c>
+      <c r="B546" t="s" s="2">
         <v>1981</v>
       </c>
-      <c r="B546" t="s" s="2">
+      <c r="C546" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D546" t="s" s="2">
         <v>1982</v>
       </c>
-      <c r="C546" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D546" t="s" s="2">
+      <c r="E546" t="s" s="2">
         <v>1983</v>
-      </c>
-      <c r="E546" t="s" s="2">
-        <v>1984</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
+        <v>1984</v>
+      </c>
+      <c r="B547" t="s" s="2">
         <v>1985</v>
       </c>
-      <c r="B547" t="s" s="2">
+      <c r="C547" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D547" t="s" s="2">
         <v>1986</v>
       </c>
-      <c r="C547" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D547" t="s" s="2">
-        <v>1987</v>
-      </c>
       <c r="E547" t="s" s="2">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
+        <v>1987</v>
+      </c>
+      <c r="B548" t="s" s="2">
         <v>1988</v>
       </c>
-      <c r="B548" t="s" s="2">
+      <c r="C548" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D548" t="s" s="2">
         <v>1989</v>
       </c>
-      <c r="C548" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D548" t="s" s="2">
+      <c r="E548" t="s" s="2">
         <v>1990</v>
-      </c>
-      <c r="E548" t="s" s="2">
-        <v>1991</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
+        <v>1991</v>
+      </c>
+      <c r="B549" t="s" s="2">
         <v>1992</v>
       </c>
-      <c r="B549" t="s" s="2">
+      <c r="C549" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D549" t="s" s="2">
         <v>1993</v>
       </c>
-      <c r="C549" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D549" t="s" s="2">
+      <c r="E549" t="s" s="2">
         <v>1994</v>
-      </c>
-      <c r="E549" t="s" s="2">
-        <v>1995</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
+        <v>1995</v>
+      </c>
+      <c r="B550" t="s" s="2">
         <v>1996</v>
       </c>
-      <c r="B550" t="s" s="2">
+      <c r="C550" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D550" t="s" s="2">
         <v>1997</v>
       </c>
-      <c r="C550" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D550" t="s" s="2">
+      <c r="E550" t="s" s="2">
         <v>1998</v>
-      </c>
-      <c r="E550" t="s" s="2">
-        <v>1999</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
+        <v>1999</v>
+      </c>
+      <c r="B551" t="s" s="2">
         <v>2000</v>
       </c>
-      <c r="B551" t="s" s="2">
+      <c r="C551" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D551" t="s" s="2">
         <v>2001</v>
       </c>
-      <c r="C551" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D551" t="s" s="2">
+      <c r="E551" t="s" s="2">
         <v>2002</v>
-      </c>
-      <c r="E551" t="s" s="2">
-        <v>2003</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
+        <v>2003</v>
+      </c>
+      <c r="B552" t="s" s="2">
         <v>2004</v>
       </c>
-      <c r="B552" t="s" s="2">
+      <c r="C552" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D552" t="s" s="2">
         <v>2005</v>
       </c>
-      <c r="C552" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D552" t="s" s="2">
+      <c r="E552" t="s" s="2">
         <v>2006</v>
-      </c>
-      <c r="E552" t="s" s="2">
-        <v>2007</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
+        <v>2007</v>
+      </c>
+      <c r="B553" t="s" s="2">
         <v>2008</v>
       </c>
-      <c r="B553" t="s" s="2">
+      <c r="C553" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D553" t="s" s="2">
         <v>2009</v>
       </c>
-      <c r="C553" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D553" t="s" s="2">
-        <v>2010</v>
-      </c>
       <c r="E553" t="s" s="2">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B554" t="s" s="2">
         <v>2011</v>
       </c>
-      <c r="B554" t="s" s="2">
+      <c r="C554" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D554" t="s" s="2">
         <v>2012</v>
       </c>
-      <c r="C554" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D554" t="s" s="2">
+      <c r="E554" t="s" s="2">
         <v>2013</v>
-      </c>
-      <c r="E554" t="s" s="2">
-        <v>2014</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B555" t="s" s="2">
         <v>2015</v>
       </c>
-      <c r="B555" t="s" s="2">
+      <c r="C555" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D555" t="s" s="2">
         <v>2016</v>
       </c>
-      <c r="C555" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D555" t="s" s="2">
-        <v>2017</v>
-      </c>
       <c r="E555" t="s" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
+        <v>2017</v>
+      </c>
+      <c r="B556" t="s" s="2">
         <v>2018</v>
       </c>
-      <c r="B556" t="s" s="2">
+      <c r="C556" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D556" t="s" s="2">
         <v>2019</v>
       </c>
-      <c r="C556" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D556" t="s" s="2">
+      <c r="E556" t="s" s="2">
         <v>2020</v>
-      </c>
-      <c r="E556" t="s" s="2">
-        <v>2021</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B557" t="s" s="2">
         <v>2022</v>
       </c>
-      <c r="B557" t="s" s="2">
+      <c r="C557" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D557" t="s" s="2">
         <v>2023</v>
       </c>
-      <c r="C557" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D557" t="s" s="2">
+      <c r="E557" t="s" s="2">
         <v>2024</v>
-      </c>
-      <c r="E557" t="s" s="2">
-        <v>2025</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B558" t="s" s="2">
         <v>2026</v>
       </c>
-      <c r="B558" t="s" s="2">
+      <c r="C558" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D558" t="s" s="2">
         <v>2027</v>
       </c>
-      <c r="C558" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D558" t="s" s="2">
+      <c r="E558" t="s" s="2">
         <v>2028</v>
-      </c>
-      <c r="E558" t="s" s="2">
-        <v>2029</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
+        <v>2029</v>
+      </c>
+      <c r="B559" t="s" s="2">
         <v>2030</v>
       </c>
-      <c r="B559" t="s" s="2">
+      <c r="C559" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D559" t="s" s="2">
         <v>2031</v>
       </c>
-      <c r="C559" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D559" t="s" s="2">
+      <c r="E559" t="s" s="2">
         <v>2032</v>
-      </c>
-      <c r="E559" t="s" s="2">
-        <v>2033</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
+        <v>2033</v>
+      </c>
+      <c r="B560" t="s" s="2">
         <v>2034</v>
       </c>
-      <c r="B560" t="s" s="2">
+      <c r="C560" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D560" t="s" s="2">
         <v>2035</v>
       </c>
-      <c r="C560" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D560" t="s" s="2">
+      <c r="E560" t="s" s="2">
         <v>2036</v>
-      </c>
-      <c r="E560" t="s" s="2">
-        <v>2037</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
+        <v>2037</v>
+      </c>
+      <c r="B561" t="s" s="2">
         <v>2038</v>
       </c>
-      <c r="B561" t="s" s="2">
+      <c r="C561" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D561" t="s" s="2">
         <v>2039</v>
       </c>
-      <c r="C561" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D561" t="s" s="2">
+      <c r="E561" t="s" s="2">
         <v>2040</v>
-      </c>
-      <c r="E561" t="s" s="2">
-        <v>2041</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
+        <v>2041</v>
+      </c>
+      <c r="B562" t="s" s="2">
         <v>2042</v>
       </c>
-      <c r="B562" t="s" s="2">
+      <c r="C562" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D562" t="s" s="2">
         <v>2043</v>
       </c>
-      <c r="C562" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D562" t="s" s="2">
+      <c r="E562" t="s" s="2">
         <v>2044</v>
-      </c>
-      <c r="E562" t="s" s="2">
-        <v>2045</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
+        <v>2045</v>
+      </c>
+      <c r="B563" t="s" s="2">
         <v>2046</v>
       </c>
-      <c r="B563" t="s" s="2">
+      <c r="C563" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D563" t="s" s="2">
         <v>2047</v>
       </c>
-      <c r="C563" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D563" t="s" s="2">
-        <v>2048</v>
-      </c>
       <c r="E563" t="s" s="2">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
+        <v>2048</v>
+      </c>
+      <c r="B564" t="s" s="2">
         <v>2049</v>
       </c>
-      <c r="B564" t="s" s="2">
+      <c r="C564" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D564" t="s" s="2">
         <v>2050</v>
       </c>
-      <c r="C564" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D564" t="s" s="2">
+      <c r="E564" t="s" s="2">
         <v>2051</v>
-      </c>
-      <c r="E564" t="s" s="2">
-        <v>2052</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
+        <v>2052</v>
+      </c>
+      <c r="B565" t="s" s="2">
         <v>2053</v>
       </c>
-      <c r="B565" t="s" s="2">
+      <c r="C565" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D565" t="s" s="2">
         <v>2054</v>
       </c>
-      <c r="C565" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D565" t="s" s="2">
+      <c r="E565" t="s" s="2">
         <v>2055</v>
-      </c>
-      <c r="E565" t="s" s="2">
-        <v>2056</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
+        <v>2056</v>
+      </c>
+      <c r="B566" t="s" s="2">
         <v>2057</v>
       </c>
-      <c r="B566" t="s" s="2">
+      <c r="C566" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D566" t="s" s="2">
         <v>2058</v>
       </c>
-      <c r="C566" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D566" t="s" s="2">
+      <c r="E566" t="s" s="2">
         <v>2059</v>
-      </c>
-      <c r="E566" t="s" s="2">
-        <v>2060</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
+        <v>2060</v>
+      </c>
+      <c r="B567" t="s" s="2">
         <v>2061</v>
-      </c>
-      <c r="B567" t="s" s="2">
-        <v>2062</v>
       </c>
       <c r="C567" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D567" t="s" s="2">
+        <v>2062</v>
+      </c>
+      <c r="E567" t="s" s="2">
         <v>2063</v>
-      </c>
-      <c r="E567" t="s" s="2">
-        <v>2064</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
+        <v>2064</v>
+      </c>
+      <c r="B568" t="s" s="2">
         <v>2065</v>
       </c>
-      <c r="B568" t="s" s="2">
+      <c r="C568" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D568" t="s" s="2">
         <v>2066</v>
       </c>
-      <c r="C568" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D568" t="s" s="2">
+      <c r="E568" t="s" s="2">
         <v>2067</v>
-      </c>
-      <c r="E568" t="s" s="2">
-        <v>2068</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
+        <v>2068</v>
+      </c>
+      <c r="B569" t="s" s="2">
         <v>2069</v>
       </c>
-      <c r="B569" t="s" s="2">
+      <c r="C569" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D569" t="s" s="2">
         <v>2070</v>
       </c>
-      <c r="C569" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D569" t="s" s="2">
+      <c r="E569" t="s" s="2">
         <v>2071</v>
-      </c>
-      <c r="E569" t="s" s="2">
-        <v>2072</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
+        <v>2072</v>
+      </c>
+      <c r="B570" t="s" s="2">
         <v>2073</v>
-      </c>
-      <c r="B570" t="s" s="2">
-        <v>2074</v>
       </c>
       <c r="C570" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D570" t="s" s="2">
+        <v>2074</v>
+      </c>
+      <c r="E570" t="s" s="2">
         <v>2075</v>
-      </c>
-      <c r="E570" t="s" s="2">
-        <v>2076</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
+        <v>2076</v>
+      </c>
+      <c r="B571" t="s" s="2">
         <v>2077</v>
       </c>
-      <c r="B571" t="s" s="2">
+      <c r="C571" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D571" t="s" s="2">
         <v>2078</v>
       </c>
-      <c r="C571" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D571" t="s" s="2">
+      <c r="E571" t="s" s="2">
         <v>2079</v>
-      </c>
-      <c r="E571" t="s" s="2">
-        <v>2080</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
+        <v>2080</v>
+      </c>
+      <c r="B572" t="s" s="2">
         <v>2081</v>
       </c>
-      <c r="B572" t="s" s="2">
+      <c r="C572" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D572" t="s" s="2">
         <v>2082</v>
       </c>
-      <c r="C572" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D572" t="s" s="2">
+      <c r="E572" t="s" s="2">
         <v>2083</v>
-      </c>
-      <c r="E572" t="s" s="2">
-        <v>2084</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
+        <v>2084</v>
+      </c>
+      <c r="B573" t="s" s="2">
         <v>2085</v>
       </c>
-      <c r="B573" t="s" s="2">
+      <c r="C573" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D573" t="s" s="2">
         <v>2086</v>
       </c>
-      <c r="C573" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D573" t="s" s="2">
-        <v>2087</v>
-      </c>
       <c r="E573" t="s" s="2">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
+        <v>2087</v>
+      </c>
+      <c r="B574" t="s" s="2">
         <v>2088</v>
       </c>
-      <c r="B574" t="s" s="2">
+      <c r="C574" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D574" t="s" s="2">
         <v>2089</v>
       </c>
-      <c r="C574" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D574" t="s" s="2">
+      <c r="E574" t="s" s="2">
         <v>2090</v>
-      </c>
-      <c r="E574" t="s" s="2">
-        <v>2091</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
+        <v>2091</v>
+      </c>
+      <c r="B575" t="s" s="2">
         <v>2092</v>
       </c>
-      <c r="B575" t="s" s="2">
+      <c r="C575" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D575" t="s" s="2">
         <v>2093</v>
       </c>
-      <c r="C575" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D575" t="s" s="2">
+      <c r="E575" t="s" s="2">
         <v>2094</v>
-      </c>
-      <c r="E575" t="s" s="2">
-        <v>2095</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
+        <v>2095</v>
+      </c>
+      <c r="B576" t="s" s="2">
         <v>2096</v>
       </c>
-      <c r="B576" t="s" s="2">
+      <c r="C576" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D576" t="s" s="2">
         <v>2097</v>
       </c>
-      <c r="C576" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D576" t="s" s="2">
+      <c r="E576" t="s" s="2">
         <v>2098</v>
-      </c>
-      <c r="E576" t="s" s="2">
-        <v>2099</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
+        <v>2099</v>
+      </c>
+      <c r="B577" t="s" s="2">
         <v>2100</v>
       </c>
-      <c r="B577" t="s" s="2">
+      <c r="C577" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D577" t="s" s="2">
         <v>2101</v>
       </c>
-      <c r="C577" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D577" t="s" s="2">
+      <c r="E577" t="s" s="2">
         <v>2102</v>
-      </c>
-      <c r="E577" t="s" s="2">
-        <v>2103</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
+        <v>2103</v>
+      </c>
+      <c r="B578" t="s" s="2">
         <v>2104</v>
       </c>
-      <c r="B578" t="s" s="2">
+      <c r="C578" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D578" t="s" s="2">
         <v>2105</v>
       </c>
-      <c r="C578" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D578" t="s" s="2">
+      <c r="E578" t="s" s="2">
         <v>2106</v>
-      </c>
-      <c r="E578" t="s" s="2">
-        <v>2107</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
+        <v>2107</v>
+      </c>
+      <c r="B579" t="s" s="2">
         <v>2108</v>
-      </c>
-      <c r="B579" t="s" s="2">
-        <v>2109</v>
       </c>
       <c r="C579" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D579" t="s" s="2">
+        <v>2109</v>
+      </c>
+      <c r="E579" t="s" s="2">
         <v>2110</v>
-      </c>
-      <c r="E579" t="s" s="2">
-        <v>2111</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
+        <v>2111</v>
+      </c>
+      <c r="B580" t="s" s="2">
         <v>2112</v>
       </c>
-      <c r="B580" t="s" s="2">
+      <c r="C580" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D580" t="s" s="2">
         <v>2113</v>
       </c>
-      <c r="C580" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D580" t="s" s="2">
+      <c r="E580" t="s" s="2">
         <v>2114</v>
-      </c>
-      <c r="E580" t="s" s="2">
-        <v>2115</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
+        <v>2115</v>
+      </c>
+      <c r="B581" t="s" s="2">
         <v>2116</v>
       </c>
-      <c r="B581" t="s" s="2">
+      <c r="C581" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D581" t="s" s="2">
         <v>2117</v>
       </c>
-      <c r="C581" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D581" t="s" s="2">
+      <c r="E581" t="s" s="2">
         <v>2118</v>
-      </c>
-      <c r="E581" t="s" s="2">
-        <v>2119</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
+        <v>2119</v>
+      </c>
+      <c r="B582" t="s" s="2">
         <v>2120</v>
       </c>
-      <c r="B582" t="s" s="2">
+      <c r="C582" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D582" t="s" s="2">
         <v>2121</v>
       </c>
-      <c r="C582" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D582" t="s" s="2">
+      <c r="E582" t="s" s="2">
         <v>2122</v>
-      </c>
-      <c r="E582" t="s" s="2">
-        <v>2123</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
+        <v>2123</v>
+      </c>
+      <c r="B583" t="s" s="2">
         <v>2124</v>
       </c>
-      <c r="B583" t="s" s="2">
+      <c r="C583" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D583" t="s" s="2">
         <v>2125</v>
       </c>
-      <c r="C583" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D583" t="s" s="2">
+      <c r="E583" t="s" s="2">
         <v>2126</v>
-      </c>
-      <c r="E583" t="s" s="2">
-        <v>2127</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
+        <v>2127</v>
+      </c>
+      <c r="B584" t="s" s="2">
         <v>2128</v>
       </c>
-      <c r="B584" t="s" s="2">
+      <c r="C584" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D584" t="s" s="2">
         <v>2129</v>
       </c>
-      <c r="C584" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D584" t="s" s="2">
-        <v>2130</v>
-      </c>
       <c r="E584" t="s" s="2">
-        <v>2129</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
+        <v>2130</v>
+      </c>
+      <c r="B585" t="s" s="2">
         <v>2131</v>
       </c>
-      <c r="B585" t="s" s="2">
+      <c r="C585" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D585" t="s" s="2">
         <v>2132</v>
       </c>
-      <c r="C585" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D585" t="s" s="2">
+      <c r="E585" t="s" s="2">
         <v>2133</v>
-      </c>
-      <c r="E585" t="s" s="2">
-        <v>2134</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
+        <v>2134</v>
+      </c>
+      <c r="B586" t="s" s="2">
         <v>2135</v>
       </c>
-      <c r="B586" t="s" s="2">
+      <c r="C586" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D586" t="s" s="2">
         <v>2136</v>
       </c>
-      <c r="C586" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D586" t="s" s="2">
-        <v>2137</v>
-      </c>
       <c r="E586" t="s" s="2">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
+        <v>2137</v>
+      </c>
+      <c r="B587" t="s" s="2">
         <v>2138</v>
       </c>
-      <c r="B587" t="s" s="2">
+      <c r="C587" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D587" t="s" s="2">
         <v>2139</v>
       </c>
-      <c r="C587" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D587" t="s" s="2">
+      <c r="E587" t="s" s="2">
         <v>2140</v>
-      </c>
-      <c r="E587" t="s" s="2">
-        <v>2141</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
+        <v>2141</v>
+      </c>
+      <c r="B588" t="s" s="2">
         <v>2142</v>
       </c>
-      <c r="B588" t="s" s="2">
+      <c r="C588" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D588" t="s" s="2">
         <v>2143</v>
       </c>
-      <c r="C588" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D588" t="s" s="2">
+      <c r="E588" t="s" s="2">
         <v>2144</v>
-      </c>
-      <c r="E588" t="s" s="2">
-        <v>2145</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
+        <v>2145</v>
+      </c>
+      <c r="B589" t="s" s="2">
         <v>2146</v>
       </c>
-      <c r="B589" t="s" s="2">
+      <c r="C589" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D589" t="s" s="2">
         <v>2147</v>
       </c>
-      <c r="C589" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D589" t="s" s="2">
+      <c r="E589" t="s" s="2">
         <v>2148</v>
-      </c>
-      <c r="E589" t="s" s="2">
-        <v>2149</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
+        <v>2149</v>
+      </c>
+      <c r="B590" t="s" s="2">
         <v>2150</v>
-      </c>
-      <c r="B590" t="s" s="2">
-        <v>2151</v>
       </c>
       <c r="C590" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D590" t="s" s="2">
+        <v>2151</v>
+      </c>
+      <c r="E590" t="s" s="2">
         <v>2152</v>
-      </c>
-      <c r="E590" t="s" s="2">
-        <v>2153</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
+        <v>2153</v>
+      </c>
+      <c r="B591" t="s" s="2">
         <v>2154</v>
       </c>
-      <c r="B591" t="s" s="2">
+      <c r="C591" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D591" t="s" s="2">
         <v>2155</v>
       </c>
-      <c r="C591" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D591" t="s" s="2">
+      <c r="E591" t="s" s="2">
         <v>2156</v>
-      </c>
-      <c r="E591" t="s" s="2">
-        <v>2157</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
+        <v>2157</v>
+      </c>
+      <c r="B592" t="s" s="2">
         <v>2158</v>
       </c>
-      <c r="B592" t="s" s="2">
+      <c r="C592" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D592" t="s" s="2">
         <v>2159</v>
       </c>
-      <c r="C592" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D592" t="s" s="2">
+      <c r="E592" t="s" s="2">
         <v>2160</v>
-      </c>
-      <c r="E592" t="s" s="2">
-        <v>2161</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
+        <v>2161</v>
+      </c>
+      <c r="B593" t="s" s="2">
         <v>2162</v>
       </c>
-      <c r="B593" t="s" s="2">
+      <c r="C593" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D593" t="s" s="2">
         <v>2163</v>
       </c>
-      <c r="C593" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D593" t="s" s="2">
+      <c r="E593" t="s" s="2">
         <v>2164</v>
-      </c>
-      <c r="E593" t="s" s="2">
-        <v>2165</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
+        <v>2165</v>
+      </c>
+      <c r="B594" t="s" s="2">
         <v>2166</v>
       </c>
-      <c r="B594" t="s" s="2">
+      <c r="C594" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D594" t="s" s="2">
         <v>2167</v>
       </c>
-      <c r="C594" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D594" t="s" s="2">
+      <c r="E594" t="s" s="2">
         <v>2168</v>
-      </c>
-      <c r="E594" t="s" s="2">
-        <v>2169</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
+        <v>2169</v>
+      </c>
+      <c r="B595" t="s" s="2">
         <v>2170</v>
       </c>
-      <c r="B595" t="s" s="2">
+      <c r="C595" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D595" t="s" s="2">
         <v>2171</v>
       </c>
-      <c r="C595" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D595" t="s" s="2">
+      <c r="E595" t="s" s="2">
         <v>2172</v>
-      </c>
-      <c r="E595" t="s" s="2">
-        <v>2173</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
+        <v>2173</v>
+      </c>
+      <c r="B596" t="s" s="2">
         <v>2174</v>
       </c>
-      <c r="B596" t="s" s="2">
+      <c r="C596" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D596" t="s" s="2">
         <v>2175</v>
       </c>
-      <c r="C596" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D596" t="s" s="2">
+      <c r="E596" t="s" s="2">
         <v>2176</v>
-      </c>
-      <c r="E596" t="s" s="2">
-        <v>2177</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
+        <v>2177</v>
+      </c>
+      <c r="B597" t="s" s="2">
         <v>2178</v>
       </c>
-      <c r="B597" t="s" s="2">
+      <c r="C597" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D597" t="s" s="2">
         <v>2179</v>
       </c>
-      <c r="C597" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D597" t="s" s="2">
+      <c r="E597" t="s" s="2">
         <v>2180</v>
-      </c>
-      <c r="E597" t="s" s="2">
-        <v>2181</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
+        <v>2181</v>
+      </c>
+      <c r="B598" t="s" s="2">
         <v>2182</v>
       </c>
-      <c r="B598" t="s" s="2">
+      <c r="C598" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D598" t="s" s="2">
         <v>2183</v>
       </c>
-      <c r="C598" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D598" t="s" s="2">
-        <v>2184</v>
-      </c>
       <c r="E598" t="s" s="2">
-        <v>2183</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
+        <v>2184</v>
+      </c>
+      <c r="B599" t="s" s="2">
         <v>2185</v>
-      </c>
-      <c r="B599" t="s" s="2">
-        <v>2186</v>
       </c>
       <c r="C599" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D599" t="s" s="2">
+        <v>2186</v>
+      </c>
+      <c r="E599" t="s" s="2">
         <v>2187</v>
-      </c>
-      <c r="E599" t="s" s="2">
-        <v>2188</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
+        <v>2188</v>
+      </c>
+      <c r="B600" t="s" s="2">
         <v>2189</v>
       </c>
-      <c r="B600" t="s" s="2">
+      <c r="C600" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D600" t="s" s="2">
         <v>2190</v>
       </c>
-      <c r="C600" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D600" t="s" s="2">
+      <c r="E600" t="s" s="2">
         <v>2191</v>
-      </c>
-      <c r="E600" t="s" s="2">
-        <v>2192</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="s" s="2">
+        <v>2192</v>
+      </c>
+      <c r="B601" t="s" s="2">
         <v>2193</v>
       </c>
-      <c r="B601" t="s" s="2">
+      <c r="C601" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D601" t="s" s="2">
         <v>2194</v>
       </c>
-      <c r="C601" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D601" t="s" s="2">
+      <c r="E601" t="s" s="2">
         <v>2195</v>
-      </c>
-      <c r="E601" t="s" s="2">
-        <v>2196</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="s" s="2">
+        <v>2196</v>
+      </c>
+      <c r="B602" t="s" s="2">
         <v>2197</v>
       </c>
-      <c r="B602" t="s" s="2">
+      <c r="C602" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D602" t="s" s="2">
         <v>2198</v>
       </c>
-      <c r="C602" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D602" t="s" s="2">
-        <v>2199</v>
-      </c>
       <c r="E602" t="s" s="2">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="s" s="2">
+        <v>2199</v>
+      </c>
+      <c r="B603" t="s" s="2">
         <v>2200</v>
       </c>
-      <c r="B603" t="s" s="2">
+      <c r="C603" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D603" t="s" s="2">
         <v>2201</v>
       </c>
-      <c r="C603" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D603" t="s" s="2">
-        <v>2202</v>
-      </c>
       <c r="E603" t="s" s="2">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="s" s="2">
+        <v>2202</v>
+      </c>
+      <c r="B604" t="s" s="2">
         <v>2203</v>
       </c>
-      <c r="B604" t="s" s="2">
+      <c r="C604" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D604" t="s" s="2">
         <v>2204</v>
       </c>
-      <c r="C604" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D604" t="s" s="2">
+      <c r="E604" t="s" s="2">
         <v>2205</v>
-      </c>
-      <c r="E604" t="s" s="2">
-        <v>2206</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="s" s="2">
+        <v>2206</v>
+      </c>
+      <c r="B605" t="s" s="2">
         <v>2207</v>
       </c>
-      <c r="B605" t="s" s="2">
+      <c r="C605" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D605" t="s" s="2">
         <v>2208</v>
       </c>
-      <c r="C605" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D605" t="s" s="2">
+      <c r="E605" t="s" s="2">
         <v>2209</v>
-      </c>
-      <c r="E605" t="s" s="2">
-        <v>2210</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s" s="2">
+        <v>2210</v>
+      </c>
+      <c r="B606" t="s" s="2">
         <v>2211</v>
       </c>
-      <c r="B606" t="s" s="2">
+      <c r="C606" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D606" t="s" s="2">
         <v>2212</v>
       </c>
-      <c r="C606" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D606" t="s" s="2">
+      <c r="E606" t="s" s="2">
         <v>2213</v>
-      </c>
-      <c r="E606" t="s" s="2">
-        <v>2214</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="s" s="2">
+        <v>2214</v>
+      </c>
+      <c r="B607" t="s" s="2">
         <v>2215</v>
       </c>
-      <c r="B607" t="s" s="2">
+      <c r="C607" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D607" t="s" s="2">
         <v>2216</v>
       </c>
-      <c r="C607" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D607" t="s" s="2">
-        <v>2217</v>
-      </c>
       <c r="E607" t="s" s="2">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="s" s="2">
+        <v>2217</v>
+      </c>
+      <c r="B608" t="s" s="2">
         <v>2218</v>
       </c>
-      <c r="B608" t="s" s="2">
+      <c r="C608" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D608" t="s" s="2">
         <v>2219</v>
       </c>
-      <c r="C608" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D608" t="s" s="2">
+      <c r="E608" t="s" s="2">
         <v>2220</v>
-      </c>
-      <c r="E608" t="s" s="2">
-        <v>2221</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="s" s="2">
+        <v>2221</v>
+      </c>
+      <c r="B609" t="s" s="2">
         <v>2222</v>
-      </c>
-      <c r="B609" t="s" s="2">
-        <v>2223</v>
       </c>
       <c r="C609" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D609" t="s" s="2">
+        <v>2223</v>
+      </c>
+      <c r="E609" t="s" s="2">
         <v>2224</v>
-      </c>
-      <c r="E609" t="s" s="2">
-        <v>2225</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="s" s="2">
+        <v>2225</v>
+      </c>
+      <c r="B610" t="s" s="2">
         <v>2226</v>
       </c>
-      <c r="B610" t="s" s="2">
+      <c r="C610" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D610" t="s" s="2">
         <v>2227</v>
       </c>
-      <c r="C610" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D610" t="s" s="2">
+      <c r="E610" t="s" s="2">
         <v>2228</v>
-      </c>
-      <c r="E610" t="s" s="2">
-        <v>2229</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="s" s="2">
+        <v>2229</v>
+      </c>
+      <c r="B611" t="s" s="2">
         <v>2230</v>
       </c>
-      <c r="B611" t="s" s="2">
+      <c r="C611" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D611" t="s" s="2">
         <v>2231</v>
       </c>
-      <c r="C611" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D611" t="s" s="2">
+      <c r="E611" t="s" s="2">
         <v>2232</v>
-      </c>
-      <c r="E611" t="s" s="2">
-        <v>2233</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="s" s="2">
+        <v>2233</v>
+      </c>
+      <c r="B612" t="s" s="2">
         <v>2234</v>
       </c>
-      <c r="B612" t="s" s="2">
+      <c r="C612" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D612" t="s" s="2">
         <v>2235</v>
       </c>
-      <c r="C612" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D612" t="s" s="2">
-        <v>2236</v>
-      </c>
       <c r="E612" t="s" s="2">
-        <v>2235</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="s" s="2">
+        <v>2236</v>
+      </c>
+      <c r="B613" t="s" s="2">
         <v>2237</v>
       </c>
-      <c r="B613" t="s" s="2">
+      <c r="C613" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D613" t="s" s="2">
         <v>2238</v>
       </c>
-      <c r="C613" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D613" t="s" s="2">
+      <c r="E613" t="s" s="2">
         <v>2239</v>
-      </c>
-      <c r="E613" t="s" s="2">
-        <v>2240</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="s" s="2">
+        <v>2240</v>
+      </c>
+      <c r="B614" t="s" s="2">
         <v>2241</v>
       </c>
-      <c r="B614" t="s" s="2">
+      <c r="C614" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D614" t="s" s="2">
         <v>2242</v>
       </c>
-      <c r="C614" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D614" t="s" s="2">
-        <v>2243</v>
-      </c>
       <c r="E614" t="s" s="2">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="s" s="2">
+        <v>2243</v>
+      </c>
+      <c r="B615" t="s" s="2">
         <v>2244</v>
       </c>
-      <c r="B615" t="s" s="2">
+      <c r="C615" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D615" t="s" s="2">
         <v>2245</v>
       </c>
-      <c r="C615" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D615" t="s" s="2">
+      <c r="E615" t="s" s="2">
         <v>2246</v>
-      </c>
-      <c r="E615" t="s" s="2">
-        <v>2247</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="s" s="2">
+        <v>2247</v>
+      </c>
+      <c r="B616" t="s" s="2">
         <v>2248</v>
       </c>
-      <c r="B616" t="s" s="2">
+      <c r="C616" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D616" t="s" s="2">
         <v>2249</v>
       </c>
-      <c r="C616" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D616" t="s" s="2">
+      <c r="E616" t="s" s="2">
         <v>2250</v>
-      </c>
-      <c r="E616" t="s" s="2">
-        <v>2251</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="s" s="2">
+        <v>2251</v>
+      </c>
+      <c r="B617" t="s" s="2">
         <v>2252</v>
       </c>
-      <c r="B617" t="s" s="2">
+      <c r="C617" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D617" t="s" s="2">
         <v>2253</v>
       </c>
-      <c r="C617" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D617" t="s" s="2">
+      <c r="E617" t="s" s="2">
         <v>2254</v>
-      </c>
-      <c r="E617" t="s" s="2">
-        <v>2255</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="s" s="2">
+        <v>2255</v>
+      </c>
+      <c r="B618" t="s" s="2">
         <v>2256</v>
-      </c>
-      <c r="B618" t="s" s="2">
-        <v>2257</v>
       </c>
       <c r="C618" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D618" t="s" s="2">
+        <v>2257</v>
+      </c>
+      <c r="E618" t="s" s="2">
         <v>2258</v>
-      </c>
-      <c r="E618" t="s" s="2">
-        <v>2259</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="s" s="2">
+        <v>2259</v>
+      </c>
+      <c r="B619" t="s" s="2">
         <v>2260</v>
       </c>
-      <c r="B619" t="s" s="2">
+      <c r="C619" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D619" t="s" s="2">
         <v>2261</v>
       </c>
-      <c r="C619" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D619" t="s" s="2">
-        <v>2262</v>
-      </c>
       <c r="E619" t="s" s="2">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="s" s="2">
+        <v>2262</v>
+      </c>
+      <c r="B620" t="s" s="2">
         <v>2263</v>
       </c>
-      <c r="B620" t="s" s="2">
+      <c r="C620" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D620" t="s" s="2">
         <v>2264</v>
       </c>
-      <c r="C620" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D620" t="s" s="2">
+      <c r="E620" t="s" s="2">
         <v>2265</v>
-      </c>
-      <c r="E620" t="s" s="2">
-        <v>2266</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="s" s="2">
+        <v>2266</v>
+      </c>
+      <c r="B621" t="s" s="2">
         <v>2267</v>
       </c>
-      <c r="B621" t="s" s="2">
+      <c r="C621" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D621" t="s" s="2">
         <v>2268</v>
       </c>
-      <c r="C621" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D621" t="s" s="2">
+      <c r="E621" t="s" s="2">
         <v>2269</v>
-      </c>
-      <c r="E621" t="s" s="2">
-        <v>2270</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="s" s="2">
+        <v>2270</v>
+      </c>
+      <c r="B622" t="s" s="2">
         <v>2271</v>
       </c>
-      <c r="B622" t="s" s="2">
+      <c r="C622" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D622" t="s" s="2">
         <v>2272</v>
       </c>
-      <c r="C622" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D622" t="s" s="2">
-        <v>2273</v>
-      </c>
       <c r="E622" t="s" s="2">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="s" s="2">
+        <v>2273</v>
+      </c>
+      <c r="B623" t="s" s="2">
         <v>2274</v>
       </c>
-      <c r="B623" t="s" s="2">
+      <c r="C623" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D623" t="s" s="2">
         <v>2275</v>
       </c>
-      <c r="C623" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D623" t="s" s="2">
+      <c r="E623" t="s" s="2">
         <v>2276</v>
-      </c>
-      <c r="E623" t="s" s="2">
-        <v>2277</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="s" s="2">
+        <v>2277</v>
+      </c>
+      <c r="B624" t="s" s="2">
         <v>2278</v>
       </c>
-      <c r="B624" t="s" s="2">
+      <c r="C624" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D624" t="s" s="2">
         <v>2279</v>
       </c>
-      <c r="C624" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D624" t="s" s="2">
+      <c r="E624" t="s" s="2">
         <v>2280</v>
-      </c>
-      <c r="E624" t="s" s="2">
-        <v>2281</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="s" s="2">
+        <v>2281</v>
+      </c>
+      <c r="B625" t="s" s="2">
         <v>2282</v>
       </c>
-      <c r="B625" t="s" s="2">
+      <c r="C625" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D625" t="s" s="2">
         <v>2283</v>
       </c>
-      <c r="C625" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D625" t="s" s="2">
+      <c r="E625" t="s" s="2">
         <v>2284</v>
-      </c>
-      <c r="E625" t="s" s="2">
-        <v>2285</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="s" s="2">
+        <v>2285</v>
+      </c>
+      <c r="B626" t="s" s="2">
         <v>2286</v>
       </c>
-      <c r="B626" t="s" s="2">
+      <c r="C626" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D626" t="s" s="2">
         <v>2287</v>
       </c>
-      <c r="C626" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D626" t="s" s="2">
-        <v>2288</v>
-      </c>
       <c r="E626" t="s" s="2">
-        <v>2287</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="s" s="2">
+        <v>2288</v>
+      </c>
+      <c r="B627" t="s" s="2">
         <v>2289</v>
       </c>
-      <c r="B627" t="s" s="2">
+      <c r="C627" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D627" t="s" s="2">
         <v>2290</v>
       </c>
-      <c r="C627" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D627" t="s" s="2">
-        <v>2291</v>
-      </c>
       <c r="E627" t="s" s="2">
-        <v>2290</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="s" s="2">
+        <v>2291</v>
+      </c>
+      <c r="B628" t="s" s="2">
         <v>2292</v>
       </c>
-      <c r="B628" t="s" s="2">
+      <c r="C628" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D628" t="s" s="2">
         <v>2293</v>
       </c>
-      <c r="C628" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D628" t="s" s="2">
+      <c r="E628" t="s" s="2">
         <v>2294</v>
-      </c>
-      <c r="E628" t="s" s="2">
-        <v>2295</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="s" s="2">
+        <v>2295</v>
+      </c>
+      <c r="B629" t="s" s="2">
         <v>2296</v>
       </c>
-      <c r="B629" t="s" s="2">
+      <c r="C629" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D629" t="s" s="2">
         <v>2297</v>
       </c>
-      <c r="C629" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D629" t="s" s="2">
+      <c r="E629" t="s" s="2">
         <v>2298</v>
-      </c>
-      <c r="E629" t="s" s="2">
-        <v>2299</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="s" s="2">
+        <v>2299</v>
+      </c>
+      <c r="B630" t="s" s="2">
         <v>2300</v>
       </c>
-      <c r="B630" t="s" s="2">
+      <c r="C630" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D630" t="s" s="2">
         <v>2301</v>
       </c>
-      <c r="C630" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D630" t="s" s="2">
-        <v>2302</v>
-      </c>
       <c r="E630" t="s" s="2">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="s" s="2">
+        <v>2302</v>
+      </c>
+      <c r="B631" t="s" s="2">
         <v>2303</v>
       </c>
-      <c r="B631" t="s" s="2">
+      <c r="C631" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D631" t="s" s="2">
         <v>2304</v>
       </c>
-      <c r="C631" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D631" t="s" s="2">
+      <c r="E631" t="s" s="2">
         <v>2305</v>
-      </c>
-      <c r="E631" t="s" s="2">
-        <v>2306</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="s" s="2">
+        <v>2306</v>
+      </c>
+      <c r="B632" t="s" s="2">
         <v>2307</v>
       </c>
-      <c r="B632" t="s" s="2">
+      <c r="C632" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D632" t="s" s="2">
         <v>2308</v>
       </c>
-      <c r="C632" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D632" t="s" s="2">
+      <c r="E632" t="s" s="2">
         <v>2309</v>
-      </c>
-      <c r="E632" t="s" s="2">
-        <v>2310</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="s" s="2">
+        <v>2310</v>
+      </c>
+      <c r="B633" t="s" s="2">
         <v>2311</v>
       </c>
-      <c r="B633" t="s" s="2">
+      <c r="C633" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D633" t="s" s="2">
         <v>2312</v>
       </c>
-      <c r="C633" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D633" t="s" s="2">
+      <c r="E633" t="s" s="2">
         <v>2313</v>
-      </c>
-      <c r="E633" t="s" s="2">
-        <v>2314</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="s" s="2">
+        <v>2314</v>
+      </c>
+      <c r="B634" t="s" s="2">
         <v>2315</v>
       </c>
-      <c r="B634" t="s" s="2">
+      <c r="C634" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D634" t="s" s="2">
         <v>2316</v>
       </c>
-      <c r="C634" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D634" t="s" s="2">
+      <c r="E634" t="s" s="2">
         <v>2317</v>
-      </c>
-      <c r="E634" t="s" s="2">
-        <v>2318</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="s" s="2">
+        <v>2318</v>
+      </c>
+      <c r="B635" t="s" s="2">
         <v>2319</v>
       </c>
-      <c r="B635" t="s" s="2">
+      <c r="C635" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D635" t="s" s="2">
         <v>2320</v>
       </c>
-      <c r="C635" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D635" t="s" s="2">
+      <c r="E635" t="s" s="2">
         <v>2321</v>
-      </c>
-      <c r="E635" t="s" s="2">
-        <v>2322</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="s" s="2">
+        <v>2322</v>
+      </c>
+      <c r="B636" t="s" s="2">
         <v>2323</v>
       </c>
-      <c r="B636" t="s" s="2">
+      <c r="C636" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D636" t="s" s="2">
         <v>2324</v>
       </c>
-      <c r="C636" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D636" t="s" s="2">
-        <v>2325</v>
-      </c>
       <c r="E636" t="s" s="2">
-        <v>2324</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="s" s="2">
+        <v>2325</v>
+      </c>
+      <c r="B637" t="s" s="2">
         <v>2326</v>
       </c>
-      <c r="B637" t="s" s="2">
+      <c r="C637" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D637" t="s" s="2">
         <v>2327</v>
       </c>
-      <c r="C637" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D637" t="s" s="2">
+      <c r="E637" t="s" s="2">
         <v>2328</v>
-      </c>
-      <c r="E637" t="s" s="2">
-        <v>2329</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="s" s="2">
+        <v>2329</v>
+      </c>
+      <c r="B638" t="s" s="2">
         <v>2330</v>
       </c>
-      <c r="B638" t="s" s="2">
+      <c r="C638" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D638" t="s" s="2">
         <v>2331</v>
       </c>
-      <c r="C638" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D638" t="s" s="2">
+      <c r="E638" t="s" s="2">
         <v>2332</v>
-      </c>
-      <c r="E638" t="s" s="2">
-        <v>2333</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="s" s="2">
+        <v>2333</v>
+      </c>
+      <c r="B639" t="s" s="2">
         <v>2334</v>
       </c>
-      <c r="B639" t="s" s="2">
+      <c r="C639" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D639" t="s" s="2">
         <v>2335</v>
       </c>
-      <c r="C639" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D639" t="s" s="2">
-        <v>2336</v>
-      </c>
       <c r="E639" t="s" s="2">
-        <v>2335</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="s" s="2">
+        <v>2336</v>
+      </c>
+      <c r="B640" t="s" s="2">
         <v>2337</v>
       </c>
-      <c r="B640" t="s" s="2">
+      <c r="C640" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D640" t="s" s="2">
         <v>2338</v>
       </c>
-      <c r="C640" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D640" t="s" s="2">
-        <v>2339</v>
-      </c>
       <c r="E640" t="s" s="2">
-        <v>2338</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="s" s="2">
+        <v>2339</v>
+      </c>
+      <c r="B641" t="s" s="2">
         <v>2340</v>
       </c>
-      <c r="B641" t="s" s="2">
+      <c r="C641" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D641" t="s" s="2">
         <v>2341</v>
       </c>
-      <c r="C641" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D641" t="s" s="2">
+      <c r="E641" t="s" s="2">
         <v>2342</v>
-      </c>
-      <c r="E641" t="s" s="2">
-        <v>2343</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="s" s="2">
+        <v>2343</v>
+      </c>
+      <c r="B642" t="s" s="2">
         <v>2344</v>
       </c>
-      <c r="B642" t="s" s="2">
+      <c r="C642" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D642" t="s" s="2">
         <v>2345</v>
       </c>
-      <c r="C642" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D642" t="s" s="2">
+      <c r="E642" t="s" s="2">
         <v>2346</v>
-      </c>
-      <c r="E642" t="s" s="2">
-        <v>2347</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="s" s="2">
+        <v>2347</v>
+      </c>
+      <c r="B643" t="s" s="2">
         <v>2348</v>
-      </c>
-      <c r="B643" t="s" s="2">
-        <v>2349</v>
       </c>
       <c r="C643" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D643" t="s" s="2">
+        <v>2349</v>
+      </c>
+      <c r="E643" t="s" s="2">
         <v>2350</v>
-      </c>
-      <c r="E643" t="s" s="2">
-        <v>2351</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="s" s="2">
+        <v>2351</v>
+      </c>
+      <c r="B644" t="s" s="2">
         <v>2352</v>
       </c>
-      <c r="B644" t="s" s="2">
+      <c r="C644" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D644" t="s" s="2">
         <v>2353</v>
       </c>
-      <c r="C644" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D644" t="s" s="2">
-        <v>2354</v>
-      </c>
       <c r="E644" t="s" s="2">
-        <v>2353</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="s" s="2">
+        <v>2354</v>
+      </c>
+      <c r="B645" t="s" s="2">
         <v>2355</v>
       </c>
-      <c r="B645" t="s" s="2">
+      <c r="C645" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D645" t="s" s="2">
         <v>2356</v>
       </c>
-      <c r="C645" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D645" t="s" s="2">
-        <v>2357</v>
-      </c>
       <c r="E645" t="s" s="2">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="s" s="2">
+        <v>2357</v>
+      </c>
+      <c r="B646" t="s" s="2">
         <v>2358</v>
       </c>
-      <c r="B646" t="s" s="2">
+      <c r="C646" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D646" t="s" s="2">
         <v>2359</v>
       </c>
-      <c r="C646" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D646" t="s" s="2">
+      <c r="E646" t="s" s="2">
         <v>2360</v>
-      </c>
-      <c r="E646" t="s" s="2">
-        <v>2361</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="s" s="2">
+        <v>2361</v>
+      </c>
+      <c r="B647" t="s" s="2">
         <v>2362</v>
-      </c>
-      <c r="B647" t="s" s="2">
-        <v>2363</v>
       </c>
       <c r="C647" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D647" t="s" s="2">
+        <v>2363</v>
+      </c>
+      <c r="E647" t="s" s="2">
         <v>2364</v>
-      </c>
-      <c r="E647" t="s" s="2">
-        <v>2365</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="s" s="2">
+        <v>2365</v>
+      </c>
+      <c r="B648" t="s" s="2">
         <v>2366</v>
-      </c>
-      <c r="B648" t="s" s="2">
-        <v>2367</v>
       </c>
       <c r="C648" t="s" s="2">
         <v>38</v>
@@ -19089,322 +19062,322 @@
     </row>
     <row r="649">
       <c r="A649" t="s" s="2">
+        <v>2367</v>
+      </c>
+      <c r="B649" t="s" s="2">
         <v>2368</v>
-      </c>
-      <c r="B649" t="s" s="2">
-        <v>2369</v>
       </c>
       <c r="C649" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D649" t="s" s="2">
+        <v>2369</v>
+      </c>
+      <c r="E649" t="s" s="2">
         <v>2370</v>
-      </c>
-      <c r="E649" t="s" s="2">
-        <v>2371</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="s" s="2">
+        <v>2371</v>
+      </c>
+      <c r="B650" t="s" s="2">
         <v>2372</v>
-      </c>
-      <c r="B650" t="s" s="2">
-        <v>2373</v>
       </c>
       <c r="C650" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D650" t="s" s="2">
+        <v>2373</v>
+      </c>
+      <c r="E650" t="s" s="2">
         <v>2374</v>
-      </c>
-      <c r="E650" t="s" s="2">
-        <v>2375</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="s" s="2">
+        <v>2375</v>
+      </c>
+      <c r="B651" t="s" s="2">
         <v>2376</v>
       </c>
-      <c r="B651" t="s" s="2">
+      <c r="C651" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D651" t="s" s="2">
         <v>2377</v>
       </c>
-      <c r="C651" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D651" t="s" s="2">
+      <c r="E651" t="s" s="2">
         <v>2378</v>
-      </c>
-      <c r="E651" t="s" s="2">
-        <v>2379</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="s" s="2">
+        <v>2379</v>
+      </c>
+      <c r="B652" t="s" s="2">
         <v>2380</v>
-      </c>
-      <c r="B652" t="s" s="2">
-        <v>2381</v>
       </c>
       <c r="C652" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D652" t="s" s="2">
+        <v>2381</v>
+      </c>
+      <c r="E652" t="s" s="2">
         <v>2382</v>
-      </c>
-      <c r="E652" t="s" s="2">
-        <v>2383</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="s" s="2">
+        <v>2383</v>
+      </c>
+      <c r="B653" t="s" s="2">
         <v>2384</v>
       </c>
-      <c r="B653" t="s" s="2">
+      <c r="C653" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D653" t="s" s="2">
         <v>2385</v>
       </c>
-      <c r="C653" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D653" t="s" s="2">
+      <c r="E653" t="s" s="2">
         <v>2386</v>
-      </c>
-      <c r="E653" t="s" s="2">
-        <v>2387</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="s" s="2">
+        <v>2387</v>
+      </c>
+      <c r="B654" t="s" s="2">
         <v>2388</v>
       </c>
-      <c r="B654" t="s" s="2">
+      <c r="C654" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D654" t="s" s="2">
         <v>2389</v>
       </c>
-      <c r="C654" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D654" t="s" s="2">
+      <c r="E654" t="s" s="2">
         <v>2390</v>
-      </c>
-      <c r="E654" t="s" s="2">
-        <v>2391</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="s" s="2">
+        <v>2391</v>
+      </c>
+      <c r="B655" t="s" s="2">
         <v>2392</v>
       </c>
-      <c r="B655" t="s" s="2">
+      <c r="C655" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D655" t="s" s="2">
         <v>2393</v>
       </c>
-      <c r="C655" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D655" t="s" s="2">
+      <c r="E655" t="s" s="2">
         <v>2394</v>
-      </c>
-      <c r="E655" t="s" s="2">
-        <v>2395</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="s" s="2">
+        <v>2395</v>
+      </c>
+      <c r="B656" t="s" s="2">
         <v>2396</v>
       </c>
-      <c r="B656" t="s" s="2">
+      <c r="C656" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D656" t="s" s="2">
         <v>2397</v>
       </c>
-      <c r="C656" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D656" t="s" s="2">
+      <c r="E656" t="s" s="2">
         <v>2398</v>
-      </c>
-      <c r="E656" t="s" s="2">
-        <v>2399</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="s" s="2">
+        <v>2399</v>
+      </c>
+      <c r="B657" t="s" s="2">
         <v>2400</v>
       </c>
-      <c r="B657" t="s" s="2">
+      <c r="C657" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D657" t="s" s="2">
         <v>2401</v>
       </c>
-      <c r="C657" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D657" t="s" s="2">
+      <c r="E657" t="s" s="2">
         <v>2402</v>
-      </c>
-      <c r="E657" t="s" s="2">
-        <v>2403</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="s" s="2">
+        <v>2403</v>
+      </c>
+      <c r="B658" t="s" s="2">
         <v>2404</v>
       </c>
-      <c r="B658" t="s" s="2">
+      <c r="C658" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D658" t="s" s="2">
         <v>2405</v>
       </c>
-      <c r="C658" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D658" t="s" s="2">
+      <c r="E658" t="s" s="2">
         <v>2406</v>
-      </c>
-      <c r="E658" t="s" s="2">
-        <v>2407</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="s" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B659" t="s" s="2">
         <v>2408</v>
       </c>
-      <c r="B659" t="s" s="2">
+      <c r="C659" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D659" t="s" s="2">
         <v>2409</v>
       </c>
-      <c r="C659" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D659" t="s" s="2">
+      <c r="E659" t="s" s="2">
         <v>2410</v>
-      </c>
-      <c r="E659" t="s" s="2">
-        <v>2411</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="s" s="2">
+        <v>2411</v>
+      </c>
+      <c r="B660" t="s" s="2">
         <v>2412</v>
       </c>
-      <c r="B660" t="s" s="2">
+      <c r="C660" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D660" t="s" s="2">
         <v>2413</v>
       </c>
-      <c r="C660" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D660" t="s" s="2">
+      <c r="E660" t="s" s="2">
         <v>2414</v>
-      </c>
-      <c r="E660" t="s" s="2">
-        <v>2415</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="s" s="2">
+        <v>2415</v>
+      </c>
+      <c r="B661" t="s" s="2">
         <v>2416</v>
       </c>
-      <c r="B661" t="s" s="2">
+      <c r="C661" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D661" t="s" s="2">
         <v>2417</v>
       </c>
-      <c r="C661" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="D661" t="s" s="2">
+      <c r="E661" t="s" s="2">
         <v>2418</v>
-      </c>
-      <c r="E661" t="s" s="2">
-        <v>2419</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="s" s="2">
+        <v>2419</v>
+      </c>
+      <c r="B662" t="s" s="2">
         <v>2420</v>
       </c>
-      <c r="B662" t="s" s="2">
+      <c r="C662" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D662" t="s" s="2">
         <v>2421</v>
       </c>
-      <c r="C662" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D662" t="s" s="2">
+      <c r="E662" t="s" s="2">
         <v>2422</v>
-      </c>
-      <c r="E662" t="s" s="2">
-        <v>2423</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="s" s="2">
+        <v>2423</v>
+      </c>
+      <c r="B663" t="s" s="2">
         <v>2424</v>
       </c>
-      <c r="B663" t="s" s="2">
+      <c r="C663" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D663" t="s" s="2">
         <v>2425</v>
       </c>
-      <c r="C663" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D663" t="s" s="2">
+      <c r="E663" t="s" s="2">
         <v>2426</v>
-      </c>
-      <c r="E663" t="s" s="2">
-        <v>2427</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="s" s="2">
+        <v>2427</v>
+      </c>
+      <c r="B664" t="s" s="2">
         <v>2428</v>
       </c>
-      <c r="B664" t="s" s="2">
+      <c r="C664" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D664" t="s" s="2">
         <v>2429</v>
       </c>
-      <c r="C664" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D664" t="s" s="2">
+      <c r="E664" t="s" s="2">
         <v>2430</v>
-      </c>
-      <c r="E664" t="s" s="2">
-        <v>2431</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="s" s="2">
+        <v>2431</v>
+      </c>
+      <c r="B665" t="s" s="2">
         <v>2432</v>
-      </c>
-      <c r="B665" t="s" s="2">
-        <v>2433</v>
       </c>
       <c r="C665" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D665" t="s" s="2">
+        <v>2433</v>
+      </c>
+      <c r="E665" t="s" s="2">
         <v>2434</v>
-      </c>
-      <c r="E665" t="s" s="2">
-        <v>2435</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="s" s="2">
+        <v>2435</v>
+      </c>
+      <c r="B666" t="s" s="2">
         <v>2436</v>
       </c>
-      <c r="B666" t="s" s="2">
+      <c r="C666" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D666" t="s" s="2">
         <v>2437</v>
       </c>
-      <c r="C666" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D666" t="s" s="2">
-        <v>2438</v>
-      </c>
       <c r="E666" t="s" s="2">
-        <v>2439</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s" s="2">
+        <v>2438</v>
+      </c>
+      <c r="B667" t="s" s="2">
+        <v>2439</v>
+      </c>
+      <c r="C667" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D667" t="s" s="2">
         <v>2440</v>
-      </c>
-      <c r="B667" t="s" s="2">
-        <v>2441</v>
-      </c>
-      <c r="C667" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D667" t="s" s="2">
-        <v>2442</v>
       </c>
       <c r="E667" t="s" s="2">
         <v>2441</v>
@@ -19412,33 +19385,33 @@
     </row>
     <row r="668">
       <c r="A668" t="s" s="2">
+        <v>2442</v>
+      </c>
+      <c r="B668" t="s" s="2">
         <v>2443</v>
       </c>
-      <c r="B668" t="s" s="2">
+      <c r="C668" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D668" t="s" s="2">
         <v>2444</v>
       </c>
-      <c r="C668" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D668" t="s" s="2">
-        <v>2445</v>
-      </c>
       <c r="E668" t="s" s="2">
-        <v>2446</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
+        <v>2445</v>
+      </c>
+      <c r="B669" t="s" s="2">
+        <v>2446</v>
+      </c>
+      <c r="C669" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D669" t="s" s="2">
         <v>2447</v>
-      </c>
-      <c r="B669" t="s" s="2">
-        <v>2448</v>
-      </c>
-      <c r="C669" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D669" t="s" s="2">
-        <v>2449</v>
       </c>
       <c r="E669" t="s" s="2">
         <v>2448</v>
@@ -19446,254 +19419,254 @@
     </row>
     <row r="670">
       <c r="A670" t="s" s="2">
+        <v>2449</v>
+      </c>
+      <c r="B670" t="s" s="2">
         <v>2450</v>
       </c>
-      <c r="B670" t="s" s="2">
+      <c r="C670" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D670" t="s" s="2">
         <v>2451</v>
       </c>
-      <c r="C670" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D670" t="s" s="2">
+      <c r="E670" t="s" s="2">
         <v>2452</v>
-      </c>
-      <c r="E670" t="s" s="2">
-        <v>2453</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="s" s="2">
+        <v>2453</v>
+      </c>
+      <c r="B671" t="s" s="2">
         <v>2454</v>
       </c>
-      <c r="B671" t="s" s="2">
+      <c r="C671" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D671" t="s" s="2">
         <v>2455</v>
       </c>
-      <c r="C671" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D671" t="s" s="2">
+      <c r="E671" t="s" s="2">
         <v>2456</v>
-      </c>
-      <c r="E671" t="s" s="2">
-        <v>2457</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="s" s="2">
+        <v>2457</v>
+      </c>
+      <c r="B672" t="s" s="2">
         <v>2458</v>
       </c>
-      <c r="B672" t="s" s="2">
+      <c r="C672" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D672" t="s" s="2">
         <v>2459</v>
       </c>
-      <c r="C672" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D672" t="s" s="2">
+      <c r="E672" t="s" s="2">
         <v>2460</v>
-      </c>
-      <c r="E672" t="s" s="2">
-        <v>2461</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="s" s="2">
+        <v>2461</v>
+      </c>
+      <c r="B673" t="s" s="2">
         <v>2462</v>
       </c>
-      <c r="B673" t="s" s="2">
+      <c r="C673" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D673" t="s" s="2">
         <v>2463</v>
       </c>
-      <c r="C673" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D673" t="s" s="2">
+      <c r="E673" t="s" s="2">
         <v>2464</v>
-      </c>
-      <c r="E673" t="s" s="2">
-        <v>2465</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="s" s="2">
+        <v>2465</v>
+      </c>
+      <c r="B674" t="s" s="2">
         <v>2466</v>
       </c>
-      <c r="B674" t="s" s="2">
+      <c r="C674" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D674" t="s" s="2">
         <v>2467</v>
       </c>
-      <c r="C674" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D674" t="s" s="2">
+      <c r="E674" t="s" s="2">
         <v>2468</v>
-      </c>
-      <c r="E674" t="s" s="2">
-        <v>2469</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="s" s="2">
+        <v>2469</v>
+      </c>
+      <c r="B675" t="s" s="2">
         <v>2470</v>
-      </c>
-      <c r="B675" t="s" s="2">
-        <v>2471</v>
       </c>
       <c r="C675" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D675" t="s" s="2">
-        <v>2472</v>
+        <v>2467</v>
       </c>
       <c r="E675" t="s" s="2">
-        <v>2473</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s" s="2">
+        <v>2471</v>
+      </c>
+      <c r="B676" t="s" s="2">
+        <v>2472</v>
+      </c>
+      <c r="C676" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D676" t="s" s="2">
+        <v>2473</v>
+      </c>
+      <c r="E676" t="s" s="2">
         <v>2474</v>
-      </c>
-      <c r="B676" t="s" s="2">
-        <v>2475</v>
-      </c>
-      <c r="C676" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="D676" t="s" s="2">
-        <v>2472</v>
-      </c>
-      <c r="E676" t="s" s="2">
-        <v>2473</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="s" s="2">
+        <v>2475</v>
+      </c>
+      <c r="B677" t="s" s="2">
         <v>2476</v>
       </c>
-      <c r="B677" t="s" s="2">
+      <c r="C677" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D677" t="s" s="2">
         <v>2477</v>
       </c>
-      <c r="C677" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D677" t="s" s="2">
+      <c r="E677" t="s" s="2">
         <v>2478</v>
-      </c>
-      <c r="E677" t="s" s="2">
-        <v>2479</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="s" s="2">
+        <v>2479</v>
+      </c>
+      <c r="B678" t="s" s="2">
         <v>2480</v>
       </c>
-      <c r="B678" t="s" s="2">
+      <c r="C678" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D678" t="s" s="2">
         <v>2481</v>
       </c>
-      <c r="C678" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D678" t="s" s="2">
+      <c r="E678" t="s" s="2">
         <v>2482</v>
-      </c>
-      <c r="E678" t="s" s="2">
-        <v>2483</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="s" s="2">
+        <v>2483</v>
+      </c>
+      <c r="B679" t="s" s="2">
         <v>2484</v>
       </c>
-      <c r="B679" t="s" s="2">
-        <v>2485</v>
-      </c>
       <c r="C679" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D679" t="s" s="2">
-        <v>2486</v>
+        <v>2467</v>
       </c>
       <c r="E679" t="s" s="2">
-        <v>2487</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s" s="2">
-        <v>2488</v>
+        <v>2485</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>2489</v>
+        <v>2486</v>
       </c>
       <c r="C680" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D680" t="s" s="2">
-        <v>2472</v>
+        <v>2467</v>
       </c>
       <c r="E680" t="s" s="2">
-        <v>2473</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s" s="2">
+        <v>2487</v>
+      </c>
+      <c r="B681" t="s" s="2">
+        <v>2488</v>
+      </c>
+      <c r="C681" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D681" t="s" s="2">
+        <v>2489</v>
+      </c>
+      <c r="E681" t="s" s="2">
         <v>2490</v>
-      </c>
-      <c r="B681" t="s" s="2">
-        <v>2491</v>
-      </c>
-      <c r="C681" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="D681" t="s" s="2">
-        <v>2472</v>
-      </c>
-      <c r="E681" t="s" s="2">
-        <v>2473</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="s" s="2">
+        <v>2491</v>
+      </c>
+      <c r="B682" t="s" s="2">
         <v>2492</v>
       </c>
-      <c r="B682" t="s" s="2">
+      <c r="C682" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D682" t="s" s="2">
         <v>2493</v>
       </c>
-      <c r="C682" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D682" t="s" s="2">
+      <c r="E682" t="s" s="2">
         <v>2494</v>
-      </c>
-      <c r="E682" t="s" s="2">
-        <v>2495</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="s" s="2">
+        <v>2495</v>
+      </c>
+      <c r="B683" t="s" s="2">
         <v>2496</v>
       </c>
-      <c r="B683" t="s" s="2">
+      <c r="C683" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D683" t="s" s="2">
         <v>2497</v>
       </c>
-      <c r="C683" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D683" t="s" s="2">
-        <v>2498</v>
-      </c>
       <c r="E683" t="s" s="2">
-        <v>2499</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s" s="2">
+        <v>2498</v>
+      </c>
+      <c r="B684" t="s" s="2">
+        <v>2499</v>
+      </c>
+      <c r="C684" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D684" t="s" s="2">
         <v>2500</v>
-      </c>
-      <c r="B684" t="s" s="2">
-        <v>2501</v>
-      </c>
-      <c r="C684" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D684" t="s" s="2">
-        <v>2502</v>
       </c>
       <c r="E684" t="s" s="2">
         <v>2501</v>
@@ -19701,444 +19674,427 @@
     </row>
     <row r="685">
       <c r="A685" t="s" s="2">
+        <v>2502</v>
+      </c>
+      <c r="B685" t="s" s="2">
         <v>2503</v>
       </c>
-      <c r="B685" t="s" s="2">
-        <v>2504</v>
-      </c>
       <c r="C685" t="s" s="2">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="D685" t="s" s="2">
-        <v>2505</v>
+        <v>156</v>
       </c>
       <c r="E685" t="s" s="2">
-        <v>2506</v>
+        <v>157</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="s" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B686" t="s" s="2">
+        <v>2505</v>
+      </c>
+      <c r="C686" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D686" t="s" s="2">
+        <v>2506</v>
+      </c>
+      <c r="E686" t="s" s="2">
         <v>2507</v>
-      </c>
-      <c r="B686" t="s" s="2">
-        <v>2508</v>
-      </c>
-      <c r="C686" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D686" t="s" s="2">
-        <v>2509</v>
-      </c>
-      <c r="E686" t="s" s="2">
-        <v>2510</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s" s="2">
-        <v>2511</v>
+        <v>2508</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>2512</v>
+        <v>2509</v>
       </c>
       <c r="C687" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D687" t="s" s="2">
-        <v>2513</v>
+        <v>2510</v>
       </c>
       <c r="E687" t="s" s="2">
-        <v>2514</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>2515</v>
+        <v>2512</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>2516</v>
+        <v>2513</v>
       </c>
       <c r="C688" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D688" t="s" s="2">
-        <v>2517</v>
+        <v>2514</v>
       </c>
       <c r="E688" t="s" s="2">
-        <v>2518</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>2519</v>
+        <v>2516</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>2520</v>
+        <v>2517</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D689" t="s" s="2">
-        <v>2521</v>
+        <v>1187</v>
       </c>
       <c r="E689" t="s" s="2">
-        <v>2522</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>2523</v>
+        <v>2518</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>2524</v>
+        <v>2519</v>
       </c>
       <c r="C690" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D690" t="s" s="2">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="E690" t="s" s="2">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>2525</v>
+        <v>2520</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>2526</v>
+        <v>2521</v>
       </c>
       <c r="C691" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D691" t="s" s="2">
-        <v>1190</v>
+        <v>2522</v>
       </c>
       <c r="E691" t="s" s="2">
-        <v>1189</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
+        <v>2524</v>
+      </c>
+      <c r="B692" t="s" s="2">
+        <v>2525</v>
+      </c>
+      <c r="C692" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D692" t="s" s="2">
+        <v>2526</v>
+      </c>
+      <c r="E692" t="s" s="2">
         <v>2527</v>
-      </c>
-      <c r="B692" t="s" s="2">
-        <v>2528</v>
-      </c>
-      <c r="C692" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D692" t="s" s="2">
-        <v>2529</v>
-      </c>
-      <c r="E692" t="s" s="2">
-        <v>2530</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="C693" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D693" t="s" s="2">
-        <v>2533</v>
+        <v>1752</v>
       </c>
       <c r="E693" t="s" s="2">
-        <v>2534</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>2535</v>
+        <v>2530</v>
       </c>
       <c r="B694" t="s" s="2">
-        <v>2536</v>
+        <v>2531</v>
       </c>
       <c r="C694" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D694" t="s" s="2">
-        <v>2537</v>
+        <v>2532</v>
       </c>
       <c r="E694" t="s" s="2">
-        <v>2538</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>2539</v>
+        <v>2534</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>2540</v>
+        <v>2535</v>
       </c>
       <c r="C695" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D695" t="s" s="2">
-        <v>2541</v>
+        <v>2536</v>
       </c>
       <c r="E695" t="s" s="2">
-        <v>2542</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>2543</v>
+        <v>2537</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>2544</v>
+        <v>2538</v>
       </c>
       <c r="C696" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D696" t="s" s="2">
-        <v>2545</v>
+        <v>2539</v>
       </c>
       <c r="E696" t="s" s="2">
-        <v>2544</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>2546</v>
+        <v>2540</v>
       </c>
       <c r="B697" t="s" s="2">
-        <v>2547</v>
+        <v>2541</v>
       </c>
       <c r="C697" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D697" t="s" s="2">
-        <v>2548</v>
+        <v>2109</v>
       </c>
       <c r="E697" t="s" s="2">
-        <v>2547</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>2549</v>
+        <v>2542</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>2550</v>
+        <v>2543</v>
       </c>
       <c r="C698" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D698" t="s" s="2">
-        <v>2110</v>
+        <v>2544</v>
       </c>
       <c r="E698" t="s" s="2">
-        <v>2111</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>2552</v>
+        <v>2547</v>
       </c>
       <c r="C699" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D699" t="s" s="2">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="E699" t="s" s="2">
-        <v>2554</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>2555</v>
+        <v>2550</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>2556</v>
+        <v>2551</v>
       </c>
       <c r="C700" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D700" t="s" s="2">
-        <v>2557</v>
+        <v>2552</v>
       </c>
       <c r="E700" t="s" s="2">
-        <v>2558</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>2559</v>
+        <v>2554</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>2560</v>
+        <v>2555</v>
       </c>
       <c r="C701" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D701" t="s" s="2">
-        <v>2561</v>
+        <v>2556</v>
       </c>
       <c r="E701" t="s" s="2">
-        <v>2562</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>2563</v>
+        <v>2557</v>
       </c>
       <c r="B702" t="s" s="2">
-        <v>2564</v>
+        <v>2558</v>
       </c>
       <c r="C702" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D702" t="s" s="2">
-        <v>2565</v>
+        <v>2559</v>
       </c>
       <c r="E702" t="s" s="2">
-        <v>2564</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>2566</v>
+        <v>2561</v>
       </c>
       <c r="B703" t="s" s="2">
-        <v>2567</v>
+        <v>2562</v>
       </c>
       <c r="C703" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D703" t="s" s="2">
-        <v>2568</v>
+        <v>2563</v>
       </c>
       <c r="E703" t="s" s="2">
-        <v>2569</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>2570</v>
+        <v>2565</v>
       </c>
       <c r="B704" t="s" s="2">
-        <v>2571</v>
+        <v>2566</v>
       </c>
       <c r="C704" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D704" t="s" s="2">
-        <v>2572</v>
+        <v>2567</v>
       </c>
       <c r="E704" t="s" s="2">
-        <v>2573</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>2574</v>
+        <v>2569</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>2575</v>
+        <v>2570</v>
       </c>
       <c r="C705" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D705" t="s" s="2">
-        <v>2576</v>
+        <v>2571</v>
       </c>
       <c r="E705" t="s" s="2">
-        <v>2577</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>2578</v>
+        <v>2572</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>2579</v>
+        <v>2573</v>
       </c>
       <c r="C706" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D706" t="s" s="2">
-        <v>2580</v>
+        <v>2574</v>
       </c>
       <c r="E706" t="s" s="2">
-        <v>2579</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>2581</v>
+        <v>2576</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>2582</v>
+        <v>2577</v>
       </c>
       <c r="C707" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D707" t="s" s="2">
-        <v>2583</v>
+        <v>2578</v>
       </c>
       <c r="E707" t="s" s="2">
-        <v>2584</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>2585</v>
+        <v>2579</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>2586</v>
+        <v>2580</v>
       </c>
       <c r="C708" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D708" t="s" s="2">
-        <v>2587</v>
+        <v>2581</v>
       </c>
       <c r="E708" t="s" s="2">
-        <v>2586</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>2588</v>
+        <v>2582</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>2589</v>
+        <v>2583</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>2590</v>
+        <v>2584</v>
       </c>
       <c r="E709" t="s" s="2">
-        <v>2589</v>
-      </c>
-    </row>
-    <row r="710">
-      <c r="A710" t="s" s="2">
-        <v>2591</v>
-      </c>
-      <c r="B710" t="s" s="2">
-        <v>2592</v>
-      </c>
-      <c r="C710" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D710" t="s" s="2">
-        <v>2593</v>
-      </c>
-      <c r="E710" t="s" s="2">
-        <v>2592</v>
+        <v>2583</v>
       </c>
     </row>
   </sheetData>

--- a/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-nebenwirkung-meddra-sct.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/mii-cm-onko-nebenwirkung-meddra-sct.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3576" uniqueCount="2585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3581" uniqueCount="2593">
   <si>
     <t>Property</t>
   </si>
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://snomed.info/sct/900000000000207008/version/20250701?fhir_vs</t>
+    <t>http://snomed.info/sct/900000000000207008/version/20260501?fhir_vs</t>
   </si>
   <si>
     <t>Display</t>
@@ -120,7 +120,7 @@
     <t/>
   </si>
   <si>
-    <t>http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20250701</t>
+    <t>http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260501</t>
   </si>
   <si>
     <t>10000060</t>
@@ -5673,10 +5673,10 @@
     <t>Prostate infection</t>
   </si>
   <si>
-    <t>9713002</t>
-  </si>
-  <si>
-    <t>Prostatitis</t>
+    <t>1371408008</t>
+  </si>
+  <si>
+    <t>Infection of prostate</t>
   </si>
   <si>
     <t>10050816</t>
@@ -7176,6 +7176,18 @@
     <t>Hemorrhage of cecum</t>
   </si>
   <si>
+    <t>10065748</t>
+  </si>
+  <si>
+    <t>Urostomy site bleeding</t>
+  </si>
+  <si>
+    <t>16751421000119105</t>
+  </si>
+  <si>
+    <t>Hemorrhage of incontinent urostomy stoma</t>
+  </si>
+  <si>
     <t>10065749</t>
   </si>
   <si>
@@ -7527,6 +7539,12 @@
     <t>Intraoperative arterial injury</t>
   </si>
   <si>
+    <t>1375944001</t>
+  </si>
+  <si>
+    <t>Traumatic injury to artery during surgery</t>
+  </si>
+  <si>
     <t>10065827</t>
   </si>
   <si>
@@ -7581,10 +7599,10 @@
     <t>Intraoperative renal injury</t>
   </si>
   <si>
-    <t>40095003</t>
-  </si>
-  <si>
-    <t>Injury of kidney</t>
+    <t>1375936001</t>
+  </si>
+  <si>
+    <t>Traumatic injury to kidney during surgery</t>
   </si>
   <si>
     <t>10065847</t>
@@ -7603,6 +7621,12 @@
   </si>
   <si>
     <t>Intraoperative venous injury</t>
+  </si>
+  <si>
+    <t>1375937005</t>
+  </si>
+  <si>
+    <t>Traumatic injury to vein during surgery</t>
   </si>
   <si>
     <t>10065849</t>
@@ -8041,7 +8065,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E709"/>
+  <dimension ref="A1:E710"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -16875,7 +16899,7 @@
         <v>1885</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D520" t="s" s="2">
         <v>1886</v>
@@ -19153,7 +19177,7 @@
         <v>2388</v>
       </c>
       <c r="C654" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D654" t="s" s="2">
         <v>2389</v>
@@ -19255,7 +19279,7 @@
         <v>2412</v>
       </c>
       <c r="C660" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D660" t="s" s="2">
         <v>2413</v>
@@ -19272,7 +19296,7 @@
         <v>2416</v>
       </c>
       <c r="C661" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D661" t="s" s="2">
         <v>2417</v>
@@ -19323,7 +19347,7 @@
         <v>2428</v>
       </c>
       <c r="C664" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D664" t="s" s="2">
         <v>2429</v>
@@ -19357,30 +19381,30 @@
         <v>2436</v>
       </c>
       <c r="C666" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D666" t="s" s="2">
         <v>2437</v>
       </c>
       <c r="E666" t="s" s="2">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="s" s="2">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="B667" t="s" s="2">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="C667" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D667" t="s" s="2">
+        <v>2441</v>
+      </c>
+      <c r="E667" t="s" s="2">
         <v>2440</v>
-      </c>
-      <c r="E667" t="s" s="2">
-        <v>2441</v>
       </c>
     </row>
     <row r="668">
@@ -19397,24 +19421,24 @@
         <v>2444</v>
       </c>
       <c r="E668" t="s" s="2">
-        <v>2443</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="s" s="2">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="B669" t="s" s="2">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C669" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D669" t="s" s="2">
+        <v>2448</v>
+      </c>
+      <c r="E669" t="s" s="2">
         <v>2447</v>
-      </c>
-      <c r="E669" t="s" s="2">
-        <v>2448</v>
       </c>
     </row>
     <row r="670">
@@ -19493,7 +19517,7 @@
         <v>2466</v>
       </c>
       <c r="C674" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D674" t="s" s="2">
         <v>2467</v>
@@ -19513,27 +19537,27 @@
         <v>53</v>
       </c>
       <c r="D675" t="s" s="2">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="E675" t="s" s="2">
-        <v>2468</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="s" s="2">
+        <v>2473</v>
+      </c>
+      <c r="B676" t="s" s="2">
+        <v>2474</v>
+      </c>
+      <c r="C676" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="D676" t="s" s="2">
         <v>2471</v>
       </c>
-      <c r="B676" t="s" s="2">
+      <c r="E676" t="s" s="2">
         <v>2472</v>
-      </c>
-      <c r="C676" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="D676" t="s" s="2">
-        <v>2473</v>
-      </c>
-      <c r="E676" t="s" s="2">
-        <v>2474</v>
       </c>
     </row>
     <row r="677">
@@ -19544,7 +19568,7 @@
         <v>2476</v>
       </c>
       <c r="C677" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D677" t="s" s="2">
         <v>2477</v>
@@ -19578,47 +19602,47 @@
         <v>2484</v>
       </c>
       <c r="C679" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D679" t="s" s="2">
-        <v>2467</v>
+        <v>2485</v>
       </c>
       <c r="E679" t="s" s="2">
-        <v>2468</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="s" s="2">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="B680" t="s" s="2">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="C680" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D680" t="s" s="2">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="E680" t="s" s="2">
-        <v>2468</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="s" s="2">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="B681" t="s" s="2">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="C681" t="s" s="2">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="D681" t="s" s="2">
-        <v>2489</v>
+        <v>2471</v>
       </c>
       <c r="E681" t="s" s="2">
-        <v>2490</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="682">
@@ -19629,7 +19653,7 @@
         <v>2492</v>
       </c>
       <c r="C682" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D682" t="s" s="2">
         <v>2493</v>
@@ -19652,24 +19676,24 @@
         <v>2497</v>
       </c>
       <c r="E683" t="s" s="2">
-        <v>2496</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="s" s="2">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="B684" t="s" s="2">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="C684" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D684" t="s" s="2">
+        <v>2501</v>
+      </c>
+      <c r="E684" t="s" s="2">
         <v>2500</v>
-      </c>
-      <c r="E684" t="s" s="2">
-        <v>2501</v>
       </c>
     </row>
     <row r="685">
@@ -19680,421 +19704,438 @@
         <v>2503</v>
       </c>
       <c r="C685" t="s" s="2">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="D685" t="s" s="2">
-        <v>156</v>
+        <v>2504</v>
       </c>
       <c r="E685" t="s" s="2">
-        <v>157</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="s" s="2">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="B686" t="s" s="2">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="C686" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D686" t="s" s="2">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="E686" t="s" s="2">
-        <v>2507</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="s" s="2">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="B687" t="s" s="2">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="C687" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D687" t="s" s="2">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="E687" t="s" s="2">
-        <v>2511</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="B688" t="s" s="2">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="C688" t="s" s="2">
         <v>228</v>
       </c>
       <c r="D688" t="s" s="2">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="E688" t="s" s="2">
-        <v>2515</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="B689" t="s" s="2">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D689" t="s" s="2">
-        <v>1187</v>
+        <v>2520</v>
       </c>
       <c r="E689" t="s" s="2">
-        <v>1186</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>2518</v>
+        <v>2522</v>
       </c>
       <c r="B690" t="s" s="2">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="C690" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D690" t="s" s="2">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E690" t="s" s="2">
-        <v>1189</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="B691" t="s" s="2">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="C691" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D691" t="s" s="2">
-        <v>2522</v>
+        <v>1190</v>
       </c>
       <c r="E691" t="s" s="2">
-        <v>2523</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="B692" t="s" s="2">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="C692" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D692" t="s" s="2">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="E692" t="s" s="2">
-        <v>2527</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="C693" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D693" t="s" s="2">
-        <v>1752</v>
+        <v>2532</v>
       </c>
       <c r="E693" t="s" s="2">
-        <v>1753</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>2530</v>
+        <v>2534</v>
       </c>
       <c r="B694" t="s" s="2">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="C694" t="s" s="2">
-        <v>228</v>
+        <v>38</v>
       </c>
       <c r="D694" t="s" s="2">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="E694" t="s" s="2">
-        <v>2533</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="B695" t="s" s="2">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="C695" t="s" s="2">
-        <v>38</v>
+        <v>228</v>
       </c>
       <c r="D695" t="s" s="2">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="E695" t="s" s="2">
-        <v>2535</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>2537</v>
+        <v>2542</v>
       </c>
       <c r="B696" t="s" s="2">
-        <v>2538</v>
+        <v>2543</v>
       </c>
       <c r="C696" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D696" t="s" s="2">
-        <v>2539</v>
+        <v>2544</v>
       </c>
       <c r="E696" t="s" s="2">
-        <v>2538</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>2540</v>
+        <v>2545</v>
       </c>
       <c r="B697" t="s" s="2">
-        <v>2541</v>
+        <v>2546</v>
       </c>
       <c r="C697" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D697" t="s" s="2">
-        <v>2109</v>
+        <v>2547</v>
       </c>
       <c r="E697" t="s" s="2">
-        <v>2110</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>2542</v>
+        <v>2548</v>
       </c>
       <c r="B698" t="s" s="2">
-        <v>2543</v>
+        <v>2549</v>
       </c>
       <c r="C698" t="s" s="2">
         <v>53</v>
       </c>
       <c r="D698" t="s" s="2">
-        <v>2544</v>
+        <v>2109</v>
       </c>
       <c r="E698" t="s" s="2">
-        <v>2545</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="B699" t="s" s="2">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="C699" t="s" s="2">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D699" t="s" s="2">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="E699" t="s" s="2">
-        <v>2549</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>2550</v>
+        <v>2554</v>
       </c>
       <c r="B700" t="s" s="2">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="C700" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D700" t="s" s="2">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="E700" t="s" s="2">
-        <v>2553</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="B701" t="s" s="2">
-        <v>2555</v>
+        <v>2559</v>
       </c>
       <c r="C701" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D701" t="s" s="2">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="E701" t="s" s="2">
-        <v>2555</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>2557</v>
+        <v>2562</v>
       </c>
       <c r="B702" t="s" s="2">
-        <v>2558</v>
+        <v>2563</v>
       </c>
       <c r="C702" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D702" t="s" s="2">
-        <v>2559</v>
+        <v>2564</v>
       </c>
       <c r="E702" t="s" s="2">
-        <v>2560</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>2561</v>
+        <v>2565</v>
       </c>
       <c r="B703" t="s" s="2">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="C703" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D703" t="s" s="2">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="E703" t="s" s="2">
-        <v>2564</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="B704" t="s" s="2">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="C704" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D704" t="s" s="2">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="E704" t="s" s="2">
-        <v>2568</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>2569</v>
+        <v>2573</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="C705" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D705" t="s" s="2">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="E705" t="s" s="2">
-        <v>2570</v>
+        <v>2576</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>2572</v>
+        <v>2577</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>2573</v>
+        <v>2578</v>
       </c>
       <c r="C706" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D706" t="s" s="2">
-        <v>2574</v>
+        <v>2579</v>
       </c>
       <c r="E706" t="s" s="2">
-        <v>2575</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>2576</v>
+        <v>2580</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="C707" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D707" t="s" s="2">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="E707" t="s" s="2">
-        <v>2577</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>2579</v>
+        <v>2584</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>2580</v>
+        <v>2585</v>
       </c>
       <c r="C708" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D708" t="s" s="2">
-        <v>2581</v>
+        <v>2586</v>
       </c>
       <c r="E708" t="s" s="2">
-        <v>2580</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>2582</v>
+        <v>2587</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>2583</v>
+        <v>2588</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>2584</v>
+        <v>2589</v>
       </c>
       <c r="E709" t="s" s="2">
-        <v>2583</v>
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="s" s="2">
+        <v>2590</v>
+      </c>
+      <c r="B710" t="s" s="2">
+        <v>2591</v>
+      </c>
+      <c r="C710" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D710" t="s" s="2">
+        <v>2592</v>
+      </c>
+      <c r="E710" t="s" s="2">
+        <v>2591</v>
       </c>
     </row>
   </sheetData>
